--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135669297</v>
+        <v>136932210</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>56875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,53 +691,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tuna, Tuna, Gstr</t>
+          <t>Tuna, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593973</v>
+        <v>594210</v>
       </c>
       <c r="R2" t="n">
-        <v>6723836</v>
+        <v>6723871</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,17 +767,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Autobox 4</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,76 +802,73 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jeanette Karlsson, Åsa Duell</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135669297</t>
+          <t>https://artportalen.se/Sighting/136932210</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135669298</v>
+        <v>136932213</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>56866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tuna, Tuna, Gstr</t>
+          <t>Tuna, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594211</v>
+        <v>594210</v>
       </c>
       <c r="R3" t="n">
-        <v>6723858</v>
+        <v>6723871</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,17 +897,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Autobox 4</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,11 +932,401 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jeanette Karlsson, Åsa Duell</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932213</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136932209</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56889</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tuna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>594210</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6723871</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Autobox 4</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932209</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135669297</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tuna, Tuna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593973</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6723836</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson, Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135669297</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135669298</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tuna, Tuna, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>594211</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6723858</v>
+      </c>
+      <c r="S6" t="n">
+        <v>13</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson, Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135669298</t>
         </is>
@@ -938,6 +1336,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932210</v>
       </c>
       <c r="B2" t="n">
-        <v>56875</v>
+        <v>56888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>136932213</v>
       </c>
       <c r="B3" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>136932209</v>
       </c>
       <c r="B4" t="n">
-        <v>56889</v>
+        <v>56902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932210</v>
       </c>
       <c r="B2" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>136932213</v>
       </c>
       <c r="B3" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>136932209</v>
       </c>
       <c r="B4" t="n">
-        <v>56902</v>
+        <v>56904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932210</v>
       </c>
       <c r="B2" t="n">
-        <v>56890</v>
+        <v>56900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>136932213</v>
       </c>
       <c r="B3" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>136932209</v>
       </c>
       <c r="B4" t="n">
-        <v>56904</v>
+        <v>56914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932210</v>
       </c>
       <c r="B2" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>136932213</v>
       </c>
       <c r="B3" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>136932209</v>
       </c>
       <c r="B4" t="n">
-        <v>56914</v>
+        <v>56915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26271-2026 artfynd.xlsx
+++ b/artfynd/A 26271-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932210</v>
       </c>
       <c r="B2" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>136932213</v>
       </c>
       <c r="B3" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>136932209</v>
       </c>
       <c r="B4" t="n">
-        <v>56915</v>
+        <v>56918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
